--- a/Excel/12_SupplementaryCO2_WIP_v01.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CAC798-A118-4685-9E97-399403AFA411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7961B2A-602F-45E8-833B-2A386B42085C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="735" windowWidth="34815" windowHeight="18060" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" firstSheet="5" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Results" sheetId="13" r:id="rId3"/>
     <sheet name="Input - CO2 Use" sheetId="70" r:id="rId4"/>
     <sheet name="12.1.1-2 Supplementary CO2" sheetId="69" r:id="rId5"/>
-    <sheet name="Constants - Common" sheetId="111" r:id="rId6"/>
+    <sheet name="Constants - Common" sheetId="122" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -185,9 +188,12 @@
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.Livestock_LookupMCFState">_xlfn.LAMBDA(_xlpm.MMS,_xlpm.MMSArray,_xlpm.State,_xlpm.StateArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="5">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="5">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="5">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -199,12 +205,32 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="5">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="5">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
+    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
+    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
+    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
+    <definedName name="Step1">#REF!</definedName>
+    <definedName name="Step2">#REF!</definedName>
+    <definedName name="Step3">#REF!</definedName>
     <definedName name="SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2">_xlfn.LAMBDA(_xlpm.Q, _xlpm.Q * 10 ^ -3)</definedName>
     <definedName name="SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Q","quantity of supplementary CO2 used within the operations","kg CO2","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_LatexEquation">_xlfn.LAMBDA("E=Q\times 10^{-3}")</definedName>
@@ -1660,116 +1686,6 @@
   <dxfs count="62">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2634,6 +2550,116 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3017,6 +3043,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>12.1.1-2 Supplementary CO2</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1400" b="0">
@@ -3098,6 +3125,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Emissions from the use of supplementary CO2</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -3499,8 +3527,8 @@
       <xdr:rowOff>136127</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="872162" cy="168829"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -3664,7 +3692,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -3746,6 +3774,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -3825,16 +3873,16 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{371EB3B0-E5DE-49F4-9F8F-370B9594177E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DC28F2C4-8AF6-4785-8C6B-CEC2944CC2FD}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EC0469C-3AAC-4C25-8B45-E899791ECD1F}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{294900B6-3C87-45A7-8EDB-09A3701C2F93}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D8738CB7-C0A6-466E-AD54-75590BF18BAC}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{A05DBB6D-CE50-4268-9475-32BE9CA69194}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3843,16 +3891,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{8320C659-C167-4CAA-9C06-854A612436E9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{13B68031-FE71-4BE0-8C8E-1D599536502B}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2CBE0C09-88F8-4FC0-91F9-37AD76A1AEAA}" name="Data source">
+    <tableColumn id="1" xr3:uid="{0FC876BB-4FDA-45B1-B871-317669F4973F}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{390BA082-D34B-4509-BBAD-72ABE42C4B39}" name="Data score">
+    <tableColumn id="2" xr3:uid="{E64587BC-B612-4C18-AC5F-429A1FF42626}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3861,16 +3909,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="47" xr:uid="{D7EAD11A-DC1E-416A-A0F3-2127BEE727A4}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{54A617B9-FF3E-410C-96A5-4B66BB130A02}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D0B2F492-E516-47ED-A029-67FEF667A678}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{94E6DCBF-2F6C-4DEA-850E-1257E85423A4}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{51E6CA6F-68DC-47AB-A1BB-C75D3CA8FA3B}" name="FracWET" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{C9F029D9-51B8-4816-85D5-3441B1755CA7}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3879,7 +3927,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="48" xr:uid="{BE2E746E-A542-4963-9138-4CB3534F691E}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{448ECC07-43ED-47BD-8BF7-B67C65717D36}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3888,19 +3936,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{10155645-FDE5-446A-BDDD-C71CD77DD825}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{BB4FDCC6-81B1-46EB-A1CB-1E21FDEA30A7}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A33C56B8-DAE9-434B-8228-CD6E219067F7}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{CC0A441B-D022-4CA6-8354-A69834BFBFD8}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{415F2F98-1C0C-4F1B-A357-E4F0898F9DA1}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{40564AE7-BB66-48AF-B3BC-88D951DDE7ED}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{364F973B-700F-4051-9AE8-A5B5A5144B24}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{3A8B2D33-5F9F-460C-93FA-C0088B196858}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6B401083-C682-49B6-9293-290F6E0CCE9C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{43884D9C-CB71-47BA-ADBF-C46278659C69}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3909,16 +3957,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{F2CB8BB6-7664-477A-B6EF-EAA92A00C8A0}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{4D75122A-64DD-44AC-906A-4556B88FCA94}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0CAEDF1E-5A86-4C59-ADB4-2A63E7ABD4DD}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{814E6C27-AEC4-4F58-94DF-EB6BF6F8DEE2}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{57851871-7E08-4269-B67C-A96E5A947487}" name="FracWET" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B95AAA77-7FB1-4F2D-8530-6B063DBAAC65}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3927,16 +3975,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="50" xr:uid="{BFE0DDAE-EACA-4433-A3E7-753CE50EADFD}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A48CC38B-BA4A-461A-8A4A-F73E8E890799}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{04E57D99-757F-4374-BB84-42339A5C3083}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{22812ECF-2BDF-479B-BDD0-ABDD9D181FA2}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{92543612-DE1F-4C45-B1F2-46B34452C302}" name="EFPRP" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F6379345-454B-47D5-B6BF-10AC3FD1C963}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3945,16 +3993,16 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="51" xr:uid="{31E1F417-A09B-41DA-9456-3458FDF04264}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{2013A3BB-DB3F-4651-BAF5-B2BC62FF8643}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5C54F0C5-3505-4964-A85B-6C95900D28A5}" name="Month">
+    <tableColumn id="1" xr3:uid="{39B089BF-12E1-4543-87BC-10C6A0C6FFD9}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE5E22FE-C43A-4172-9EDB-6FE00B1DF854}" name="Season" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1F8FDC7C-6656-4185-B6E7-8E523E08EB97}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3963,7 +4011,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="52" xr:uid="{AF70AA04-1AD5-4DF8-9CC4-5F92B5EE2A0A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{CB579B7F-3F35-4411-A973-C63A8EB50780}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3983,52 +4031,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{FD606263-AC8F-4B13-96E2-C9CA0ECFC2B3}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{6ADC392C-5850-4DF1-B61E-AD89C6F0C73A}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{328E4735-CE75-4070-9C88-AE6AC281FA52}" name="MAT (ºC)" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{BB6F7FCE-22AE-4D28-A913-77E6DA4EEDBA}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AAAA9F18-86A5-4F62-9B13-8EC468FD3268}" name="Anaerobic lagoon" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{13CC30B5-CFBC-4FBD-A997-7404CA96F1DC}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{16CDDAC7-40E8-4B7E-A5A7-534574EF9960}" name="Digester / covered lagoons" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{8377B2BA-D9A3-4F3B-9CDA-463B9C7C6D0B}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BE7531C-242C-4F06-B612-2455D4071B48}" name="Liquid systems" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{8F8FE17C-A26D-4015-8DE7-8A0284CCF305}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AA6EA91-67D5-4225-8E66-D79949E45C79}" name="Daily spread" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{335544B6-26CF-4063-8B41-14ACFA814834}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A682CC91-6B5E-45D1-857C-0228079BCC7C}" name="Composting (passive windrow)" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{ED337F61-FBEF-437D-B2EA-429DF88BF98B}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{516A42DC-F452-4685-9EE1-8DB5323E888F}" name="Solid storage" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{7A316A78-DAB2-4C8A-BD7A-5BAB30008B7C}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3E59565B-237D-4BF7-8514-8C00EE69787F}" name="Pit storage" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{ED235F5C-8782-4085-ACE9-5581BEFF0447}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B94C989A-1174-49BC-8E63-5C88C372C925}" name="Deep litter" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{82BDA5BE-621D-463B-8C21-FE2122E0D19D}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4E416B5A-6B9A-4444-8C96-0603C11DC870}" name="Poultry manure with bedding" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{A89BA2F9-19A1-47F2-B204-07445F32B7EA}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{2302252A-7FB0-4046-9B12-B1CD2F1BBED4}" name="Poultry manure without bedding" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{5843EC54-CAD6-4A10-8170-CA7C4C5ED5F5}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{50CED419-50AF-49B3-8F42-E496D5B781AB}" name="Direct processing" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{8DE32C71-B502-409B-928F-750CCA16648F}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FACDE6F8-8A2F-4040-8D12-2E35D0831482}" name="Direct application" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{27CA3685-3894-4D69-B24B-CA075337B41C}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2134A83A-1EB7-471E-ADAA-05ADE14C7593}" name="Pasture range and paddock" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{99559C44-EEE8-4D8F-A9A8-FCC203F32BB3}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C3199CA-00F6-4D2D-9A1A-14E5576B6B3A}" name="MAT raw" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{66B87B0B-81DA-4A7A-9AF4-43E1B0D7455E}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4037,16 +4085,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
-  <autoFilter ref="D257:E259" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{0E617B26-18D0-4AFA-82FE-00AED0900410}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6441941C-5801-414B-9EFC-BFCD02E9AABA}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{DB5A1BF0-2654-4654-A005-25B68250353F}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFFF76A7-AEC2-426D-9FB9-7DCEAE399701}" name="EFNi &amp; EFN2Oi" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DC92C861-4FEA-4BB5-A89C-E12CFC7C9D9E}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4055,20 +4103,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3AE6144E-A1E7-4518-B032-EF188F35C422}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BFEFA86D-B928-4343-A1C3-8AACEDBA85DF}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A67EF497-7B1B-4776-9D83-A8AD1BEAF517}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{8DC65857-1762-4DED-831A-06826FC8E599}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E9614A8-2F7E-4491-9C0D-E14664D3CBD5}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{FE185B29-9557-4581-BF86-603C43AB533D}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48FCC7EC-93CF-4022-930C-DFF884BE9C3A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{2A95011F-50D1-4289-9E7F-3DF967FE98BA}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4077,12 +4125,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A98080EA-F2FB-4179-A336-59EF5AF50E8F}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4A19D36B-5E63-4974-A793-136379A355A9}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8E44BE92-8969-4CB0-B814-3C00C2C18F3C}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{9C5723D8-D0B4-4125-9BBC-4DDD424173F8}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4091,16 +4139,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{3B270221-00F4-4B48-BE2F-1F9DCAB7874A}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{94DE9EAB-5015-4060-9BC2-2CD8F0DDFF50}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D82C5D5A-F88F-46E7-868F-025402490369}" name="Gas">
+    <tableColumn id="1" xr3:uid="{4001CBA9-F4A3-4C7D-A275-B1BA3E362739}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6DC661F8-0615-4FB7-8AE2-83962657C55A}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{3AD90266-42FF-4CC8-A75A-9C805610DB6E}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4109,7 +4157,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{79E591EE-C4BF-4FA2-8F75-39DA84C25602}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C444C88D-010B-4CAA-8EC7-6D34E52C3F4A}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4118,19 +4166,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BABC03E3-165B-407A-BF04-28738E72D28A}" name="Gas">
+    <tableColumn id="1" xr3:uid="{3A8C0CFA-3DE9-498C-966D-6B244E120A7E}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CF0196FE-D2CF-4F66-8847-9CE3DB549E9B}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{92DAC899-6F8B-4D13-8C45-81CFF6F286F1}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71C50FB6-28B8-4C5F-B7F7-F9E98423215B}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{28F8688B-CF96-482A-8C40-083526955682}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9E60D175-C714-4272-922B-6384C81A6A4A}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{8770A909-8C13-47E9-AD96-8C67877643DF}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{77C6E5B1-2CB1-4714-9B60-3FC1F2C784D3}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{D670556D-4DF6-4786-BA8A-09C654C17DB9}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4139,7 +4187,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{5EB24DAD-7938-4A28-8102-A92DD6232701}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{781EDDAF-7F9B-48B0-A342-31E9122F53DD}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4159,52 +4207,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{7C646E3D-156E-438B-9E75-102B5E96E255}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{8D40750F-7330-456A-BB21-E3EFB286833F}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F6652C3-1BDE-4F33-9D5E-1BA7F24CFE1E}" name="MAT" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{62E66C4A-4479-4A17-B98A-2F53B0DF4466}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{68D3A033-0C56-472E-A3CF-B482905871CF}" name="MAP" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{B9FC8F4B-35F5-4F7B-8E1C-CE583C7FC041}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{18D7CFC5-1F89-47C0-AF12-0FD6A80AD2C8}" name="Frost days per year" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{380F7CFF-6056-41A6-BF80-BBCCEE00662F}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{694DED4D-19CA-49A7-A7A4-ED3CD36E0BA2}" name="Elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{02CC8E12-B022-4DEC-B7E6-726532DF5644}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BE47AD00-59A1-4916-A3FF-4E905492D142}" name="MAP:PET" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{115D7C7A-B275-48F4-8B1D-23731CD5E9FD}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8CD0BB0E-B9A0-4065-920B-F859089361EB}" name="Min temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{4116C12D-F410-4E10-93F9-6434C598BA9E}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9AD474F5-6F0E-4F15-87EA-A3E86BD8CD84}" name="Max temp" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{540A3023-64D8-4CEB-8D95-A6D179AA549E}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4132B96D-08DF-47B8-9134-F88DA6CBA26A}" name="Min rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{D64547E2-0462-4E06-854A-CCF17A6318D7}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{799D2CC4-68A8-4F6B-B5E8-BA9B134CD629}" name="Max rainfall" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{655EDD60-857F-42AC-A2BF-DEC3DFB090B0}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF3C7CFE-CC8F-4407-9CD2-DB7BCF735828}" name="Min frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{7278EB04-7DA4-4E3B-919C-4FEB67D4C659}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9CB12B6D-F283-41CE-A0AC-7DA70F3FEA35}" name="Max frost days" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{BE43C499-B1F6-40CB-823D-961D21AEEAA3}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{DE6B8D57-DEA5-4CDB-BEA5-6794B3B8B4C1}" name="Min elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{D03997E9-53F2-4697-B878-CFFFC9520B10}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F1C5507D-FFFD-4456-AAE0-9309987F0339}" name="Max elevation" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{C44A8FA0-40DC-4D7B-94F7-F219584A1AD7}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BB91B1DF-4B57-426B-BF6A-71715747D3B2}" name="Min MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{A2246660-C845-4D9C-9366-7ECECC01DF7C}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7674CAA3-6E67-48AA-BF62-AECA84F01CB9}" name="Max MAP:PET" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{AB61D1E6-3618-40D8-826C-ABEBBE7DF2B0}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4213,16 +4261,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{3FAC77B2-7BB0-4B78-B387-3E2D5CA67215}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{57EBC0E9-F0EE-409B-B02B-65F95E0DBD10}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9DF69629-1C76-40A4-BBA1-FB28BF754268}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{30DD4BB3-ABE2-4C86-A881-C32DBDC5DA0E}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{99A9C0E3-7924-426C-A581-5C219452362E}" name="Wet or Dry Zone" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{D6850548-4D06-4192-95CD-9B52C1BD5D14}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4231,7 +4279,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{AE4202F8-BB52-48CE-B368-8D0A44A67525}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{4DCD1AF7-0F5B-4776-A34C-5F60347B0D68}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4239,16 +4287,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4BD1B715-E9FF-4B2E-A162-3DD06FA33AAE}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{AA691C71-D51E-4A4F-8321-B70D5A2166C7}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3FDEC609-65F3-40EC-B489-B99CC8E44680}" name="MAT">
+    <tableColumn id="2" xr3:uid="{5E81B5F6-3184-4C46-B272-8A55D7855886}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{25C140A7-4F53-46DB-A6E5-3FFA5FE81DD6}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{B59D4E84-94D9-4E61-A29D-6B62F741B5BA}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C2D4126F-3B56-4A19-AD7E-FA0C2ECA0D87}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{BBD14DC8-B942-4A1D-9E63-811222BB9D53}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4257,7 +4305,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{F8066D7D-5B7A-4C2D-96C5-0B642AEDBDD8}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{E977CA12-7C95-4E57-894A-0768785E4B72}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4265,16 +4313,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CFC2CD32-0D6A-477F-9AB9-8CC735000875}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{5140A975-6A60-4280-BCE4-6B97A4BAA3EC}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66F05498-A494-40EC-A370-E31F9319F6E9}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{ABCF8B7A-FBDB-4E6C-BEA6-908DC8354C80}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0FEB24E7-52AA-4E09-8CAD-E3593BA1850C}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{64A764CC-9EBF-4E70-88E8-EA1D64C310D4}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B9588CB4-A6E3-43EF-86F2-28512F6C0466}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{94CC1A4B-3582-43CC-86D9-A0C469CEAF18}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5853,58 +5901,58 @@
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
-  <conditionalFormatting sqref="F47 F210 E200">
-    <cfRule type="cellIs" dxfId="10" priority="62" operator="lessThan">
+  <conditionalFormatting sqref="F47 E200 F210">
+    <cfRule type="cellIs" dxfId="46" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F126:F127">
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F138:F139">
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150:F151">
-    <cfRule type="cellIs" dxfId="7" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F162:F163">
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250:F251">
-    <cfRule type="cellIs" dxfId="5" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F255:F256">
-    <cfRule type="cellIs" dxfId="4" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260:F261">
-    <cfRule type="cellIs" dxfId="3" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F285">
-    <cfRule type="cellIs" dxfId="2" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289:F290">
-    <cfRule type="cellIs" dxfId="1" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294:F295">
-    <cfRule type="cellIs" dxfId="0" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6412,7 +6460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C96C07E-3BBC-40AD-9550-B73B24462357}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BDDFF2-3D95-47BA-886B-648B3235344C}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7816,31 +7864,31 @@
       </c>
       <c r="T97" s="27"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="29" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="29" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="29" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="29" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="29" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="29" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="29"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="29"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="5" t="str" cm="1">
@@ -10404,15 +10452,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -10607,7 +10646,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -10618,19 +10657,20 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADIALgAxADoAIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXABuAEUAXABuAHQAIABDAE8AMgBlAFwAbgBFAD0AUQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4AUQAgAD0AIABxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAAoAGsAZwAgAEMATwAyACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALABcAG4AIAAgACAAIABRACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAdQBzAGUAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADIALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBcACIALAAgAFwAIgBxAHUAYQBuAHQAaQB0AHkAIABvAGYAIABzAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5ACAAQwBPADIAIAB1AHMAZQBkACAAdwBpAHQAaABpAG4AIAB0AGgAZQAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAawBnACAAQwBPADIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVABpAHQAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0ACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFMAbwB1AHIAYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADEAMgAuADEAOgAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMQAyAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcAG4ARQBcAG4AdAAgAEMATwAyAGUAXABuAEUAPQBRAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBRACAAPQAgAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgACgAawBnACAAQwBPADIAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsAFwAbgAgACAAIAAgAFEAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMgAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQA9AFEAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAFwAIgAsACAAXAAiAHEAdQBhAG4AdABpAHQAeQAgAG8AZgAgAHMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAIABDAE8AMgAgAHUAcwBlAGQAIAB3AGkAdABoAGkAbgAgAHQAaABlACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBUAGkAdABsAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMgBfADEAXwAxAF8AMQBfAF8AMQBfAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAFUAbgBpAHQAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8AUwBvAHUAcgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUwB1AHAAcABsAGUAbQBlAG4AdABhAHIAeQBDAE8AMgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAyAF8AMQBfADEAXwAxAF8AXwAxAF8ARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBTAHUAcABwAGwAZQBtAGUAbgB0AGEAcgB5AEMATwAyAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADIAXwAxAF8AMQBfADEAXwBfADEAXwBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFMAdQBwAHAAbABlAG0AZQBuAHQAYQByAHkAQwBPADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10649,7 +10689,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -10660,10 +10700,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>